--- a/5/search/FY5_Missile3_results/solutions_direction_117.0.xlsx
+++ b/5/search/FY5_Missile3_results/solutions_direction_117.0.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,71 +487,281 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117</v>
+        <v>112.5</v>
       </c>
       <c r="B2" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>12186.44902446673</v>
+        <v>12375.46063838017</v>
       </c>
       <c r="F2" t="n">
-        <v>-403.3163086544448</v>
+        <v>-492.22860294158</v>
       </c>
       <c r="G2" t="n">
         <v>1300</v>
       </c>
       <c r="H2" t="n">
-        <v>12186.44902446673</v>
+        <v>12336.42692827893</v>
       </c>
       <c r="I2" t="n">
-        <v>-403.3163086544448</v>
+        <v>-397.9928906254287</v>
       </c>
       <c r="J2" t="n">
-        <v>1300</v>
+        <v>1295.1</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>108</v>
+      </c>
+      <c r="C3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12338.72302887312</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-403.5361678204965</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12338.72302887312</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-403.5361678204965</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1300</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>117</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12273.61520041673</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-574.3895612986114</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12182.81710046882</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-396.1882564609379</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1280.4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>117</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106</v>
+      </c>
+      <c r="C5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12230.03211244173</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-488.8529349765281</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12181.90911946934</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-394.4062434125611</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1295.1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>117</v>
+      </c>
+      <c r="B6" t="n">
+        <v>112</v>
+      </c>
+      <c r="C6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12186.44902446673</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-403.3163086544448</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12186.44902446673</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-403.3163086544448</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>117</v>
+      </c>
+      <c r="B7" t="n">
+        <v>130</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12291.77482040631</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-610.0298222661461</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12173.73729047402</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-378.3681259771704</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1280.4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>117</v>
+      </c>
+      <c r="B8" t="n">
+        <v>138</v>
+      </c>
+      <c r="C8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12248.19173243131</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-524.4931959440628</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12185.54104346725</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-401.534295606068</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1295.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>117</v>
+      </c>
+      <c r="B9" t="n">
         <v>140</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C9" t="n">
         <v>12</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E9" t="n">
         <v>12237.29596043756</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F9" t="n">
         <v>-503.109039363542</v>
       </c>
-      <c r="G3" t="n">
-        <v>1300</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="G9" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H9" t="n">
         <v>12173.73729047402</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I9" t="n">
         <v>-378.3681259771705</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J9" t="n">
         <v>1295.1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K9" t="n">
         <v>3</v>
       </c>
     </row>
